--- a/cleaning_pipeline_R/dictionaries/dictionary_zim_twenty_8_day_follow_up_enriched.xlsx
+++ b/cleaning_pipeline_R/dictionaries/dictionary_zim_twenty_8_day_follow_up_enriched.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t xml:space="preserve">display_label</t>
   </si>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">What Illnesses?</t>
   </si>
   <si>
-    <t xml:space="preserve">Outcome</t>
+    <t xml:space="preserve">Outcome at Discharge from facility</t>
   </si>
   <si>
     <t xml:space="preserve">NEOTREE ID</t>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t xml:space="preserve">Date and time of Birth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outcome</t>
   </si>
   <si>
     <t xml:space="preserve">NUID_S</t>
@@ -751,25 +754,25 @@
         <v>65</v>
       </c>
       <c r="AB1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AG1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2">
@@ -1441,7 +1444,7 @@
         <v>42</v>
       </c>
       <c r="AC8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD8" t="s">
         <v>42</v>
@@ -1828,7 +1831,7 @@
         <v>68</v>
       </c>
       <c r="AB12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC12" t="s">
         <v>42</v>
@@ -1843,7 +1846,7 @@
         <v>42</v>
       </c>
       <c r="AG12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH12" t="b">
         <v>1</v>
@@ -1925,10 +1928,10 @@
         <v>69</v>
       </c>
       <c r="AB13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD13" t="s">
         <v>42</v>
@@ -2025,7 +2028,7 @@
         <v>42</v>
       </c>
       <c r="AC14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AD14" t="s">
         <v>42</v>
@@ -2609,10 +2612,10 @@
         <v>70</v>
       </c>
       <c r="AB20" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC20" t="s">
         <v>74</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>73</v>
       </c>
       <c r="AD20" t="s">
         <v>42</v>
@@ -3927,7 +3930,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Outcome at discharge</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3972,10 +3975,10 @@
         <v>1</v>
       </c>
       <c r="AA34" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="AB34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC34" t="s">
         <v>42</v>
@@ -3990,7 +3993,7 @@
         <v>42</v>
       </c>
       <c r="AG34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH34" t="b">
         <v>1</v>
@@ -4069,13 +4072,13 @@
       </c>
       <c r="Z35"/>
       <c r="AA35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AC35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD35" t="s">
         <v>42</v>
@@ -5673,12 +5676,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DUM</t>
+          <t>HIVLR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Abandoned baby</t>
+          <t>HIV low risk</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -5686,12 +5689,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8be57d79-6bb9-4de8-a3a1-1d699a513f7b</t>
+          <t>243252d5-c833-4428-9ed9-ab7db1af7bc7</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DUM</t>
+          <t>HIVLR</t>
         </is>
       </c>
     </row>
@@ -5703,12 +5706,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HIVLR</t>
+          <t>HIVHR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HIV low risk</t>
+          <t>HIV high risk</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -5716,12 +5719,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>243252d5-c833-4428-9ed9-ab7db1af7bc7</t>
+          <t>4a447bcc-b8c5-4a7d-8adb-5d8dddf1172c</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HIVLR</t>
+          <t>HIVHR</t>
         </is>
       </c>
     </row>
@@ -5733,12 +5736,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HIVHR</t>
+          <t>HypogAs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HIV high risk</t>
+          <t>Hypoglycaemia (NOT symptomatic)</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -5746,12 +5749,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4a447bcc-b8c5-4a7d-8adb-5d8dddf1172c</t>
+          <t>9295fe69-649f-47b5-ba35-9cb2762bfc77</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HIVHR</t>
+          <t>HypogAs</t>
         </is>
       </c>
     </row>
@@ -5763,12 +5766,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HypogAs</t>
+          <t>HypogSy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hypoglycaemia (NOT symptomatic)</t>
+          <t>Hypoglycaemia (symptomatic)</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -5776,12 +5779,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9295fe69-649f-47b5-ba35-9cb2762bfc77</t>
+          <t>7458bc48-1b80-45fc-9c76-8bd0839d6493</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>HypogAs</t>
+          <t>HypogSy</t>
         </is>
       </c>
     </row>
@@ -5793,12 +5796,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HypogSy</t>
+          <t>HIE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hypoglycaemia (Symptomatic)</t>
+          <t>Birth Asphyxia / Hypoxic Ischaemic Encephalopathy (HIE)</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -5806,12 +5809,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7458bc48-1b80-45fc-9c76-8bd0839d6493</t>
+          <t>159642b1-956f-440b-8006-1e2672565f37</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HypogSy</t>
+          <t>HIE</t>
         </is>
       </c>
     </row>
@@ -5823,12 +5826,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HIE</t>
+          <t>GSchis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Birth Asphyxia/ Hypoxic Ischaemic Encephalopathy (HIE)</t>
+          <t>Gastroschisis</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -5836,12 +5839,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>159642b1-956f-440b-8006-1e2672565f37</t>
+          <t>8c46b45f-ca6f-428a-a990-cd0781f29953</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HIE</t>
+          <t>GSchis</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5856,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GSchis</t>
+          <t>MJ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gastroschisis</t>
+          <t>Jaundice (physiological)</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -5866,12 +5869,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8c46b45f-ca6f-428a-a990-cd0781f29953</t>
+          <t>3b00efc1-c61e-4a01-8d50-abfe0630fc7d</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GSchis</t>
+          <t>MJ</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5886,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MJ</t>
+          <t>LBW</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Physiological Jaundice</t>
+          <t>Low Birth Weight (1500-2499g)</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -5896,12 +5899,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3b00efc1-c61e-4a01-8d50-abfe0630fc7d</t>
+          <t>7a25194a-1612-4dfe-bdb0-17f6cb6f7302</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MJ</t>
+          <t>LBW</t>
         </is>
       </c>
     </row>
@@ -5913,12 +5916,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LBW</t>
+          <t>VLBW</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Low Birth Weight (1500-2499g)</t>
+          <t>Very Low Birth Weight (1000-1499g)</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -5926,12 +5929,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7a25194a-1612-4dfe-bdb0-17f6cb6f7302</t>
+          <t>5ff36144-79aa-4077-b748-9e172152e4ae</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LBW</t>
+          <t>VLBW</t>
         </is>
       </c>
     </row>
@@ -5943,12 +5946,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VLBW</t>
+          <t>ExLBW</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Very Low Birth Weight (1000-1499g)</t>
+          <t>ExtremelyLow Birth Weight (&lt;1000g)</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -5956,12 +5959,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5ff36144-79aa-4077-b748-9e172152e4ae</t>
+          <t>df4cb4a5-f815-409d-8072-327b7b3f0e4c</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VLBW</t>
+          <t>ExLBW</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5976,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ExLBW</t>
+          <t>MecEx</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ExtremelyLow Birth Weight (&lt;1000g)</t>
+          <t>Meconium exposure (not symptomatic)</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -5986,12 +5989,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>df4cb4a5-f815-409d-8072-327b7b3f0e4c</t>
+          <t>ed9e5d7b-f9b1-4037-a7bf-c53e257700ef</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ExLBW</t>
+          <t>MecEx</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6006,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MecEx</t>
+          <t>MiHypo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Meconium exposure (not symptomatic)</t>
+          <t>Mild Hypothermia</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -6016,12 +6019,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ed9e5d7b-f9b1-4037-a7bf-c53e257700ef</t>
+          <t>584d8cfd-e44b-4b7d-8b39-31dc05895d28</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MecEx</t>
+          <t>MiHypo</t>
         </is>
       </c>
     </row>
@@ -6033,12 +6036,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MiHypo</t>
+          <t>ModHypo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mild Hypothermia</t>
+          <t>Moderate Hypothermia</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -6046,12 +6049,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>584d8cfd-e44b-4b7d-8b39-31dc05895d28</t>
+          <t>0319f271-4dca-4aed-aba6-a1a33b56bceb</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MiHypo</t>
+          <t>ModHypo</t>
         </is>
       </c>
     </row>
@@ -6063,12 +6066,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ModHypo</t>
+          <t>SHypo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Moderate Hypothermia</t>
+          <t>Severe Hypothermia</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -6076,12 +6079,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0319f271-4dca-4aed-aba6-a1a33b56bceb</t>
+          <t>e8f09d3e-8959-4dfd-932d-f59a7e7d427b</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ModHypo</t>
+          <t>SHypo</t>
         </is>
       </c>
     </row>
@@ -6093,12 +6096,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SHypo</t>
+          <t>Hyperth</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Severe Hypothermia</t>
+          <t>Hyperthermia</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -6106,12 +6109,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>e8f09d3e-8959-4dfd-932d-f59a7e7d427b</t>
+          <t>8d07a953-cd26-4c54-9777-83147f22b500</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SHypo</t>
+          <t>Hyperth</t>
         </is>
       </c>
     </row>
@@ -6123,12 +6126,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hyperth</t>
+          <t>SEPS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hyperthermia</t>
+          <t>Neonatal Sepsis</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -6136,12 +6139,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8d07a953-cd26-4c54-9777-83147f22b500</t>
+          <t>daa9886a-6d27-41f8-9fe4-55021a63b18f</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hyperth</t>
+          <t>SEPS</t>
         </is>
       </c>
     </row>
@@ -6153,12 +6156,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SEPS</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Neonatal Sepsis</t>
+          <t>Risk factors for sepsis (asymptomatic baby)</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -6166,12 +6169,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>daa9886a-6d27-41f8-9fe4-55021a63b18f</t>
+          <t>36c6d337-0973-4088-bc69-1dd70ba78841</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SEPS</t>
+          <t>Risk</t>
         </is>
       </c>
     </row>
@@ -6183,12 +6186,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Risk factors for sepsis (asymptomatic baby)</t>
+          <t>Normal baby</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -6196,12 +6199,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>36c6d337-0973-4088-bc69-1dd70ba78841</t>
+          <t>368afbb3-e9c3-4105-bc68-5307f0abc5e9</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>NB</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6216,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>PN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Normal baby</t>
+          <t>Pneumonia / Bronchiolitis</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -6226,12 +6229,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>368afbb3-e9c3-4105-bc68-5307f0abc5e9</t>
+          <t>3b16402d-0c16-4725-92d6-57d3cbc1ab1a</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>PN</t>
         </is>
       </c>
     </row>
@@ -6243,12 +6246,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PN</t>
+          <t>Prem</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pneumonia / Bronchiolitis</t>
+          <t>Premature (32 to 36.6 weeks)</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -6256,12 +6259,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3b16402d-0c16-4725-92d6-57d3cbc1ab1a</t>
+          <t>9ffd995c-a13d-4b98-bc3b-e795579b6ee5</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PN</t>
+          <t>Prem</t>
         </is>
       </c>
     </row>
@@ -6273,12 +6276,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Prem</t>
+          <t>VPrem</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Premature (32 to 36.6 weeks)</t>
+          <t>Very Premature (28 to 31.6 weeks)</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -6286,12 +6289,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>9ffd995c-a13d-4b98-bc3b-e795579b6ee5</t>
+          <t>36b9b7b9-b13a-4d9e-9725-33e7d49309c4</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Prem</t>
+          <t>VPrem</t>
         </is>
       </c>
     </row>
@@ -6303,12 +6306,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>VPrem</t>
+          <t>ExPrem</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Very Premature (28-31 weeks)</t>
+          <t>Extremely Premature (&lt;28 weeks)</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -6316,12 +6319,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>36b9b7b9-b13a-4d9e-9725-33e7d49309c4</t>
+          <t>3e0413a8-4388-49d6-bfda-0e17c5d3d2cb</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>VPrem</t>
+          <t>ExPrem</t>
         </is>
       </c>
     </row>
@@ -6333,12 +6336,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ExPrem</t>
+          <t>PremRD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Extremely Premature (&lt;28 weeks)</t>
+          <t>Premature baby with Respiratory Distress</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -6346,12 +6349,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3e0413a8-4388-49d6-bfda-0e17c5d3d2cb</t>
+          <t>fee9b3a4-d019-45f0-8060-9eb706f2b2a7</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ExPrem</t>
+          <t>PremRD</t>
         </is>
       </c>
     </row>
@@ -6363,12 +6366,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PremRD</t>
+          <t>TTN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Premature baby with Respiratory Distress</t>
+          <t>Transient Tachypnoea of Newborn (TTN)</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -6376,12 +6379,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>fee9b3a4-d019-45f0-8060-9eb706f2b2a7</t>
+          <t>37b883c7-b227-4ede-a9b3-6fcacd0e528b</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PremRD</t>
+          <t>TTN</t>
         </is>
       </c>
     </row>
@@ -6393,12 +6396,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TTN</t>
+          <t>Oth</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Transient Tachypnoea of Newborn (TTN)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -6406,12 +6409,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>37b883c7-b227-4ede-a9b3-6fcacd0e528b</t>
+          <t>db05c62c-8ead-4534-812a-777c44f15582</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TTN</t>
+          <t>Oth</t>
         </is>
       </c>
     </row>
@@ -6423,12 +6426,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>TermRD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Respiratory Distress (term baby)</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -6436,12 +6439,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>db05c62c-8ead-4534-812a-777c44f15582</t>
+          <t>44ac2e73-bc9c-443b-a2f6-e12ac35bf46b</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>TermRD</t>
         </is>
       </c>
     </row>
@@ -6453,12 +6456,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TermRD</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Term with RD</t>
+          <t>Jaundice (pathological)</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -6466,12 +6469,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>44ac2e73-bc9c-443b-a2f6-e12ac35bf46b</t>
+          <t>4f630173-97e1-4698-bf7e-3bfb62ea8b0b</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TermRD</t>
+          <t>DJ</t>
         </is>
       </c>
     </row>
@@ -6483,12 +6486,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>sHIE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pathological Jaundice</t>
+          <t>Suspected Hypoxic Ischaemic Encephalopathy</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -6496,12 +6499,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4f630173-97e1-4698-bf7e-3bfb62ea8b0b</t>
+          <t>f46a6f89-69e8-4d63-bf17-7cb3cabbbd85</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>sHIE</t>
         </is>
       </c>
     </row>
@@ -6513,12 +6516,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>sHIE</t>
+          <t>ProJ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Suspected Hypoxic Ischaemic Encephalopathy</t>
+          <t>Jaundice (prolonged)</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -6526,12 +6529,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>f46a6f89-69e8-4d63-bf17-7cb3cabbbd85</t>
+          <t>67db2930-db77-4399-b3f5-58a3a7cd2324</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>sHIE</t>
+          <t>ProJ</t>
         </is>
       </c>
     </row>
@@ -6543,12 +6546,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PJaundice</t>
+          <t>CleftLip</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Prolonged Jaundice</t>
+          <t>Cleft lip</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -6556,12 +6559,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>67db2930-db77-4399-b3f5-58a3a7cd2324</t>
+          <t>914e3df7-432c-4a57-a27b-9e6b776e5b86</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PJaundice</t>
+          <t>CleftLip</t>
         </is>
       </c>
     </row>
@@ -6573,12 +6576,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CleftLip</t>
+          <t>CleftRD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cleft lip</t>
+          <t>Cleft lip and/or palate with RD</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -6586,12 +6589,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>914e3df7-432c-4a57-a27b-9e6b776e5b86</t>
+          <t>faef241d-0f6e-43a0-a9e4-81fc3b165a05</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CleftLip</t>
+          <t>CleftRD</t>
         </is>
       </c>
     </row>
@@ -6603,12 +6606,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CleftRD</t>
+          <t>CleftLipPalate</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cleft lip and/or palate with RD</t>
+          <t>Cleft lip and/or palate</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -6616,12 +6619,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>faef241d-0f6e-43a0-a9e4-81fc3b165a05</t>
+          <t>5938dbd6-1a36-467b-b8a6-d449fea26546</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CleftRD</t>
+          <t>CleftLipPalate</t>
         </is>
       </c>
     </row>
@@ -6633,12 +6636,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CleftLipPalate</t>
+          <t>Omph</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cleft lip and/or palate</t>
+          <t>Omphalocele/ Exomphalos</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -6646,12 +6649,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>5938dbd6-1a36-467b-b8a6-d449fea26546</t>
+          <t>5eabb008-c8f6-46fb-a6b2-fce26bd187ed</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CleftLipPalate</t>
+          <t>Omph</t>
         </is>
       </c>
     </row>
@@ -6663,12 +6666,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Omph</t>
+          <t>Myelo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Omphalocele/ Exomphalos</t>
+          <t>Myelomeningocele / Spina Bifida</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -6676,12 +6679,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5eabb008-c8f6-46fb-a6b2-fce26bd187ed</t>
+          <t>60ce8813-1be6-47df-84be-2239c40190ff</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Omph</t>
+          <t>Myelo</t>
         </is>
       </c>
     </row>
@@ -6693,12 +6696,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Myelo</t>
+          <t>CDH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Myelomeningocele / Spina Bifida</t>
+          <t>Congenital dislocation of the hip (CDH)</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -6706,12 +6709,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>60ce8813-1be6-47df-84be-2239c40190ff</t>
+          <t>c372101d-d0c7-44c1-bb45-4121d77643af</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Myelo</t>
+          <t>CDH</t>
         </is>
       </c>
     </row>
@@ -6723,12 +6726,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CDH</t>
+          <t>MiTalipes</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Congenital Dislocation of the hip (CDH)</t>
+          <t>Talipes MILD (club foot)</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -6736,12 +6739,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>c372101d-d0c7-44c1-bb45-4121d77643af</t>
+          <t>e3ae6e68-2aa5-4200-9d5a-738f86d68b9f</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CDH</t>
+          <t>MiTalipes</t>
         </is>
       </c>
     </row>
@@ -6753,12 +6756,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MiTalipes</t>
+          <t>MoTalipes</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mild Talipes (club foot)</t>
+          <t>Moderate Talipes (club foot)</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -6766,12 +6769,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>e3ae6e68-2aa5-4200-9d5a-738f86d68b9f</t>
+          <t>8c78b28d-b053-4841-b756-c207b84e7820</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MiTalipes</t>
+          <t>MoTalipes</t>
         </is>
       </c>
     </row>
@@ -6783,12 +6786,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MoTalipes</t>
+          <t>HYDR</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Moderate Talipes (club foot)</t>
+          <t>Hydrocephalus</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -6796,12 +6799,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>8c78b28d-b053-4841-b756-c207b84e7820</t>
+          <t>50d378a8-61e2-49f0-aaf4-90df0e41c965</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MoTalipes</t>
+          <t>HYDR</t>
         </is>
       </c>
     </row>
@@ -6813,12 +6816,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HYDR</t>
+          <t>ASP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hydrocephalus</t>
+          <t>Aspiration</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -6826,12 +6829,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>50d378a8-61e2-49f0-aaf4-90df0e41c965</t>
+          <t>4b2c7af8-0c85-4ffc-9ef0-6179e5678e57</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HYDR</t>
+          <t>ASP</t>
         </is>
       </c>
     </row>
@@ -6843,12 +6846,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ASP</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Aspiration</t>
+          <t>Meconium Aspiration</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -6856,12 +6859,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>4b2c7af8-0c85-4ffc-9ef0-6179e5678e57</t>
+          <t>64d41cbd-1af4-409d-aec2-7d8b3bea0a95</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ASP</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6876,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>Gast</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Meconium Aspiration</t>
+          <t>Gastroenteritsis/ Diarrhoea</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -6886,12 +6889,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>64d41cbd-1af4-409d-aec2-7d8b3bea0a95</t>
+          <t>04e7eb7e-35e6-4104-809a-f00509b983d0</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>Gast</t>
         </is>
       </c>
     </row>
@@ -6903,12 +6906,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gast</t>
+          <t>TOF</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gastroenteritsis/ Diarrhoea</t>
+          <t>Tracheo-oesophageal fistula</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -6916,12 +6919,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>04e7eb7e-35e6-4104-809a-f00509b983d0</t>
+          <t>d515f2c4-d39e-43ab-ba89-b14de9d86e86</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gast</t>
+          <t>TOF</t>
         </is>
       </c>
     </row>
@@ -6933,12 +6936,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TOF</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tracheo-oesophageal fistula</t>
+          <t>Necrotising Enterocolitis (NEC)</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -6946,12 +6949,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>d515f2c4-d39e-43ab-ba89-b14de9d86e86</t>
+          <t>470b83f0-119e-4d3a-b4ea-95defa57bb51</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TOF</t>
+          <t>NEC</t>
         </is>
       </c>
     </row>
@@ -6963,12 +6966,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>CongDth</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Necrotising Enterocolitis (NEC)</t>
+          <t>Congenital Abnormality incompatible with life</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -6976,12 +6979,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>470b83f0-119e-4d3a-b4ea-95defa57bb51</t>
+          <t>324f84c3-45e1-4b21-be6a-e7480b611ac1</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>CongDth</t>
         </is>
       </c>
     </row>
@@ -6993,12 +6996,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CongDth</t>
+          <t>Hypg</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Congenital Abnormality incompatible with life</t>
+          <t>Hypoglycaemia</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -7006,12 +7009,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>324f84c3-45e1-4b21-be6a-e7480b611ac1</t>
+          <t>2d5cb621-68a4-4c52-84d4-0da326bf72c1</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CongDth</t>
+          <t>Hypg</t>
         </is>
       </c>
     </row>
@@ -7023,12 +7026,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hypg</t>
+          <t>Hypo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hypoglycaemia</t>
+          <t>Hypothermia</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -7036,12 +7039,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2d5cb621-68a4-4c52-84d4-0da326bf72c1</t>
+          <t>d87c426f-1ab8-497b-ae5c-d91b2573ac16</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hypg</t>
+          <t>Hypo</t>
         </is>
       </c>
     </row>
@@ -7053,12 +7056,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hypo</t>
+          <t>EONS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hypothermia</t>
+          <t>Neonatal Sepsis - Early Onset (EONS)</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -7066,12 +7069,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>d87c426f-1ab8-497b-ae5c-d91b2573ac16</t>
+          <t>5afffeda-8bdb-4496-a48d-de45d9703a5c</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hypo</t>
+          <t>EONS</t>
         </is>
       </c>
     </row>
@@ -7083,12 +7086,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EONS</t>
+          <t>LONS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Neonatal Sepsis - Early Onset (EONS)</t>
+          <t>Neonatal Sepsis - Late Onset (LONS)</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -7096,12 +7099,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>5afffeda-8bdb-4496-a48d-de45d9703a5c</t>
+          <t>2090fdeb-89f7-4614-a428-46ef56f1a5f7</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>EONS</t>
+          <t>LONS</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7116,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LONS</t>
+          <t>DJEx</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Neonatal Sepsis - Late Onset (LONS)</t>
+          <t>Pathological jaundice (Exchange transfusion required)</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -7126,12 +7129,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2090fdeb-89f7-4614-a428-46ef56f1a5f7</t>
+          <t>0a5eddbf-c74b-4a97-bc77-af3bfdc18e7b</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LONS</t>
+          <t>DJEx</t>
         </is>
       </c>
     </row>
@@ -7143,12 +7146,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DJEx</t>
+          <t>DJPh</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pathological jaundice (Exchange transfusion required)</t>
+          <t>Pathological jaundice (phototherapy range)</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -7156,12 +7159,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0a5eddbf-c74b-4a97-bc77-af3bfdc18e7b</t>
+          <t>08191b22-46f7-4dff-9ea7-3bb76489a1d5</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>DJEx</t>
+          <t>DJPh</t>
         </is>
       </c>
     </row>
@@ -7173,12 +7176,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DJPh</t>
+          <t>Unk</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pathological jaundice (phototherapy range)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -7186,42 +7189,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>08191b22-46f7-4dff-9ea7-3bb76489a1d5</t>
+          <t>786afecb-ece6-43c3-9290-4d9f86f6a05d</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>DJPh</t>
+          <t>Unk</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>causedeath</t>
+          <t>causeofdeatknow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>786afecb-ece6-43c3-9290-4d9f86f6a05d</t>
+          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7233,55 +7236,55 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
+          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>causeofdeatknow</t>
+          <t>currcond</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>AlivWell</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Alive &amp; Well (Home)</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
+          <t>daeb9cc9-dc8f-4e5a-9368-c568ef316165</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>AlivWell</t>
         </is>
       </c>
     </row>
@@ -7293,25 +7296,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AlivWell</t>
+          <t>AlivNotWell</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Alive &amp; Well (Home)</t>
+          <t>Alive &amp; Not Well (Home)</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>daeb9cc9-dc8f-4e5a-9368-c568ef316165</t>
+          <t>166e9c0d-4ae8-412f-b8ac-20de6677cf51</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AlivWell</t>
+          <t>AlivNotWell</t>
         </is>
       </c>
     </row>
@@ -7323,25 +7326,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AlivNotWell</t>
+          <t>AlivAdmi</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Alive &amp; Not Well (Home)</t>
+          <t>Alive &amp; Admitted</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>166e9c0d-4ae8-412f-b8ac-20de6677cf51</t>
+          <t>e632b784-428a-4145-a03f-d6c707448972</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AlivNotWell</t>
+          <t>AlivAdmi</t>
         </is>
       </c>
     </row>
@@ -7353,55 +7356,55 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AlivAdmi</t>
+          <t>PassAway</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Alive &amp; Admitted</t>
+          <t>Passed Away</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>e632b784-428a-4145-a03f-d6c707448972</t>
+          <t>c6863ec4-5c3b-4b61-a09e-fbb8b4e43f67</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AlivAdmi</t>
+          <t>PassAway</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>currcond</t>
+          <t>day3chec</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PassAway</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Passed Away</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>c6863ec4-5c3b-4b61-a09e-fbb8b4e43f67</t>
+          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PassAway</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7413,55 +7416,55 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
+          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>day3chec</t>
+          <t>day7chec</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
+          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7473,55 +7476,55 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
+          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>day7chec</t>
+          <t>day7weigknow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes I Know</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
+          <t>e80d492c-255c-482c-b48a-c92f7e5939eb</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -7533,25 +7536,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yes I Know</t>
+          <t>Not Sure But Can Estimate</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>e80d492c-255c-482c-b48a-c92f7e5939eb</t>
+          <t>1de45461-94fb-4557-84d8-58013a5de7fb</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>NS</t>
         </is>
       </c>
     </row>
@@ -7563,55 +7566,55 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Not Sure But Can Estimate</t>
+          <t>No I Don't</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1de45461-94fb-4557-84d8-58013a5de7fb</t>
+          <t>80fa0e40-ea2c-4315-9002-97a0f3c617a4</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>day7weigknow</t>
+          <t>feedasse</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Form</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>No I Don't</t>
+          <t>Formula</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>80fa0e40-ea2c-4315-9002-97a0f3c617a4</t>
+          <t>66a478e5-3eb4-4bd7-afef-33d314af60b8</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Form</t>
         </is>
       </c>
     </row>
@@ -7623,25 +7626,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Form</t>
+          <t>BresMilk</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Formula</t>
+          <t>Breast Milk</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>66a478e5-3eb4-4bd7-afef-33d314af60b8</t>
+          <t>39a6c447-5acf-44b5-b356-00ec91d4c888</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Form</t>
+          <t>BresMilk</t>
         </is>
       </c>
     </row>
@@ -7653,25 +7656,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BresMilk</t>
+          <t>Wate</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Breast Milk</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>39a6c447-5acf-44b5-b356-00ec91d4c888</t>
+          <t>e81ea04e-384e-47fe-832b-83fee5a7286e</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BresMilk</t>
+          <t>Wate</t>
         </is>
       </c>
     </row>
@@ -7683,25 +7686,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Wate</t>
+          <t>CookOil</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Cooking Oil</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>e81ea04e-384e-47fe-832b-83fee5a7286e</t>
+          <t>502b356f-7c49-43c5-ac03-4bef49625d37</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wate</t>
+          <t>CookOil</t>
         </is>
       </c>
     </row>
@@ -7713,55 +7716,55 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CookOil</t>
+          <t>SoliPorr</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cooking Oil</t>
+          <t>Solids/ Porridge</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>502b356f-7c49-43c5-ac03-4bef49625d37</t>
+          <t>f8345afd-0436-471b-8484-33d36961e448</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CookOil</t>
+          <t>SoliPorr</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>feedasse</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SoliPorr</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Solids/ Porridge</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>f8345afd-0436-471b-8484-33d36961e448</t>
+          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SoliPorr</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7773,55 +7776,55 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
+          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>hosp</t>
+          <t>medigive</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
+          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7833,55 +7836,55 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
+          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>medigive</t>
+          <t>medihelp</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
+          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7893,55 +7896,55 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
+          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>medihelp</t>
+          <t>medihelptype</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>TradReli</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Traditional/Religious Help</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
+          <t>430b2b91-f7e0-47ed-b444-8fd0e3f9f283</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>TradReli</t>
         </is>
       </c>
     </row>
@@ -7953,25 +7956,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TradReli</t>
+          <t>PolyHosp</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Traditional/Religious Help</t>
+          <t>Polyclinic/Hospital</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>430b2b91-f7e0-47ed-b444-8fd0e3f9f283</t>
+          <t>a6e85b5e-53ab-4afd-ad9c-8ac897231ec6</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>TradReli</t>
+          <t>PolyHosp</t>
         </is>
       </c>
     </row>
@@ -7983,25 +7986,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PolyHosp</t>
+          <t>Pharm</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Polyclinic/Hospital</t>
+          <t>Pharmacy</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>a6e85b5e-53ab-4afd-ad9c-8ac897231ec6</t>
+          <t>3785086d-236b-4c9f-8841-e43e0089a1aa</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PolyHosp</t>
+          <t>Pharm</t>
         </is>
       </c>
     </row>
@@ -8013,25 +8016,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Pharm</t>
+          <t>TradReli</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Pharmacy</t>
+          <t>Traditional/ Religious Help</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>3785086d-236b-4c9f-8841-e43e0089a1aa</t>
+          <t>63fec619-c10b-42e8-8004-a5e4157b0126</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pharm</t>
+          <t>TradReli</t>
         </is>
       </c>
     </row>
@@ -8043,55 +8046,55 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TradReli</t>
+          <t>PolyHosp</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Traditional/ Religious Help</t>
+          <t>Polyclinic/ Hospital</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>63fec619-c10b-42e8-8004-a5e4157b0126</t>
+          <t>3584cb97-18dc-4dd5-b4c6-6981a1a5c7e9</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>TradReli</t>
+          <t>PolyHosp</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>medihelptype</t>
+          <t>neotreeoutcome</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PolyHosp</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Polyclinic/ Hospital</t>
+          <t>Discharged</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>3584cb97-18dc-4dd5-b4c6-6981a1a5c7e9</t>
+          <t>43649e79-b816-4cf5-a986-11e6fca92744</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PolyHosp</t>
+          <t>DC</t>
         </is>
       </c>
     </row>
@@ -8103,25 +8106,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>NND&lt;24</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Discharged</t>
+          <t>Death (at LESS than 24 hrs of age)</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>43649e79-b816-4cf5-a986-11e6fca92744</t>
+          <t>7e704490-b9de-4a10-be6b-0d9662619e41</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>NND&lt;24</t>
         </is>
       </c>
     </row>
@@ -8133,25 +8136,25 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NND&lt;24</t>
+          <t>NND&gt;24</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Death (at LESS than 24 hrs of age)</t>
+          <t>Death (at MORE than 24 hrs of age)</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>7e704490-b9de-4a10-be6b-0d9662619e41</t>
+          <t>f1c27f9e-f324-44ff-b8a1-9dcc6e9e978c</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>NND&lt;24</t>
+          <t>NND&gt;24</t>
         </is>
       </c>
     </row>
@@ -8163,25 +8166,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NND&gt;24</t>
+          <t>DDA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Death (at MORE than 24 hrs of age)</t>
+          <t>Died during admission</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>f1c27f9e-f324-44ff-b8a1-9dcc6e9e978c</t>
+          <t>b361d43a-3fc4-4384-9c99-162e09d3d297</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NND&gt;24</t>
+          <t>DDA</t>
         </is>
       </c>
     </row>
@@ -8193,25 +8196,25 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DDA</t>
+          <t>ABS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Died During Admission</t>
+          <t>Absconded</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>b361d43a-3fc4-4384-9c99-162e09d3d297</t>
+          <t>e4a6c032-322d-415a-82d2-6be63f9ba078</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>DDA</t>
+          <t>ABS</t>
         </is>
       </c>
     </row>
@@ -8223,25 +8226,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>TRO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Absconded</t>
+          <t>Transferred to other ward</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>e4a6c032-322d-415a-82d2-6be63f9ba078</t>
+          <t>35e526ce-3029-49a5-8690-47c25e03618f</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>TRO</t>
         </is>
       </c>
     </row>
@@ -8253,25 +8256,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>TRH</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Transferred to other ward</t>
+          <t>Transferred to other hospital</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>35e526ce-3029-49a5-8690-47c25e03618f</t>
+          <t>10a66145-08f8-4a0e-81ee-e3aadccff87f</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>TRH</t>
         </is>
       </c>
     </row>
@@ -8283,25 +8286,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TRH</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Transferred to other Hospital</t>
+          <t>Discharged on request</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>10a66145-08f8-4a0e-81ee-e3aadccff87f</t>
+          <t>4037bf4f-28f3-4ab7-b9e2-29923173d2d3</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>TRH</t>
+          <t>DCR</t>
         </is>
       </c>
     </row>
@@ -8313,25 +8316,25 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>DPC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Discharged on Request</t>
+          <t>Discharge on Palliative Care</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4037bf4f-28f3-4ab7-b9e2-29923173d2d3</t>
+          <t>3a8bd9e1-9c25-4702-abb8-699b081dd75d</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>DPC</t>
         </is>
       </c>
     </row>
@@ -8343,25 +8346,25 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DPC</t>
+          <t>NND</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Discharge on Palliative Care</t>
+          <t>Died</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>3a8bd9e1-9c25-4702-abb8-699b081dd75d</t>
+          <t>77e60ae9-6555-4cd4-9b42-0b63e6df782b</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>DPC</t>
+          <t>NND</t>
         </is>
       </c>
     </row>
@@ -8373,25 +8376,25 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NND</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Brought in dead</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>77e60ae9-6555-4cd4-9b42-0b63e6df782b</t>
+          <t>998e82df-e4a9-4b0d-9333-c08d4a64a18c</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>NND</t>
+          <t>BID</t>
         </is>
       </c>
     </row>
@@ -8403,25 +8406,25 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>STB</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brought in dead</t>
+          <t>Stillbirth</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>998e82df-e4a9-4b0d-9333-c08d4a64a18c</t>
+          <t>09789e89-d117-4568-b61e-3f9240d3c684</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>STB</t>
         </is>
       </c>
     </row>
@@ -8433,25 +8436,25 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>DAMA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Stillbirth</t>
+          <t>Discharged against medical advice</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>09789e89-d117-4568-b61e-3f9240d3c684</t>
+          <t>754ba193-f6a8-4fe5-adb5-65c7e6ad4467</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>DAMA</t>
         </is>
       </c>
     </row>
@@ -8463,25 +8466,25 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DAMA</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Discharged against medical advice</t>
+          <t>Live Birth</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>754ba193-f6a8-4fe5-adb5-65c7e6ad4467</t>
+          <t>e95c4c50-33e9-4e7b-9a43-704a5285225d</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>DAMA</t>
+          <t>LB</t>
         </is>
       </c>
     </row>
@@ -8493,25 +8496,25 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>ENND</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Live Birth</t>
+          <t>Early Neonatal Death</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>e95c4c50-33e9-4e7b-9a43-704a5285225d</t>
+          <t>f5c87ec8-ddb3-4b9b-a7b0-515aa5f6c0ba</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>ENND</t>
         </is>
       </c>
     </row>
@@ -8523,25 +8526,25 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ENND</t>
+          <t>STBM</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Early Neonatal Death</t>
+          <t>Stillbirth Macerated</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>f5c87ec8-ddb3-4b9b-a7b0-515aa5f6c0ba</t>
+          <t>69c7a0e0-84f0-435c-8ef4-bc4ad88adbc3</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ENND</t>
+          <t>STBM</t>
         </is>
       </c>
     </row>
@@ -8553,25 +8556,25 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>STBM</t>
+          <t>STBF</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Stillbirth Macerated</t>
+          <t>Stillbirth Fresh</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>69c7a0e0-84f0-435c-8ef4-bc4ad88adbc3</t>
+          <t>393d3fad-3a61-4c1e-afe5-afff5c45e75c</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>STBM</t>
+          <t>STBF</t>
         </is>
       </c>
     </row>
@@ -8583,25 +8586,25 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>STBF</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Stillbirth Fresh</t>
+          <t>Miscarriage - born with no signs of life at under 22 weeks gestation</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>393d3fad-3a61-4c1e-afe5-afff5c45e75c</t>
+          <t>d65ae47c-59a7-41c5-8c6c-f40c73fb6207</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>STBF</t>
+          <t>MISC</t>
         </is>
       </c>
     </row>
@@ -8613,25 +8616,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>STBM</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Miscarriage - born with no signs of life at under 22 weeks gestation</t>
+          <t>Stillbirth Mascerated</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>d65ae47c-59a7-41c5-8c6c-f40c73fb6207</t>
+          <t>75d3d54b-e335-406a-96eb-565856a9d590</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>STBM</t>
         </is>
       </c>
     </row>
@@ -8643,25 +8646,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>STBM</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Stillbirth Mascerated</t>
+          <t>Miscarriage - death before 22 weeks' gestation</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>75d3d54b-e335-406a-96eb-565856a9d590</t>
+          <t>87a75435-efd3-4127-a25a-5a115e69ef45</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>STBM</t>
+          <t>MISC</t>
         </is>
       </c>
     </row>
@@ -8673,55 +8676,55 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>TRO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Miscarriage - death before 22 weeks' gestation</t>
+          <t>Transferred to another ward (example: paediatric ward)</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>87a75435-efd3-4127-a25a-5a115e69ef45</t>
+          <t>509a9a6e-690a-4e06-8f57-8e37d2d4f3bd</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>TRO</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>neotreeoutcome</t>
+          <t>pretermclinatte</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Transferred to another ward (example: paediatric ward)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>509a9a6e-690a-4e06-8f57-8e37d2d4f3bd</t>
+          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -8733,55 +8736,55 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
+          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>pretermclinatte</t>
+          <t>reasquit</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Comfortable to Say</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
+          <t>e0280383-61f0-4dc7-8c7c-6053c8d92885</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -8793,25 +8796,25 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Not Comfortable to Say</t>
+          <t>Open at Another Convenient Time</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>e0280383-61f0-4dc7-8c7c-6053c8d92885</t>
+          <t>b3e04daa-d190-49a3-9514-3d1f2ce0b902</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -8823,55 +8826,55 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Open at Another Convenient Time</t>
+          <t>Other Reasons</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>b3e04daa-d190-49a3-9514-3d1f2ce0b902</t>
+          <t>dd89c636-6b17-4a20-85af-fc76eb83500f</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>reasquit</t>
+          <t>receweigknow</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Other Reasons</t>
+          <t>Yes I Know</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>dd89c636-6b17-4a20-85af-fc76eb83500f</t>
+          <t>e80d492c-255c-482c-b48a-c92f7e5939eb</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -8883,25 +8886,25 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Yes I Know</t>
+          <t>Not Sure But Can Estimate</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>e80d492c-255c-482c-b48a-c92f7e5939eb</t>
+          <t>1de45461-94fb-4557-84d8-58013a5de7fb</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>NS</t>
         </is>
       </c>
     </row>
@@ -8913,55 +8916,55 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Not Sure But Can Estimate</t>
+          <t>No I Don't</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1de45461-94fb-4557-84d8-58013a5de7fb</t>
+          <t>80fa0e40-ea2c-4315-9002-97a0f3c617a4</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>receweigknow</t>
+          <t>termpre</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>No I Don't</t>
+          <t>Full Term</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>80fa0e40-ea2c-4315-9002-97a0f3c617a4</t>
+          <t>139d02da-9ea9-43fc-97b5-a5b1d4bff017</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -8973,53 +8976,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Full Term</t>
+          <t>Pre-Term</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>139d02da-9ea9-43fc-97b5-a5b1d4bff017</t>
+          <t>75be23d7-424e-4e56-91d2-804fc9333842</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>termpre</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Pre-Term</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>2</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>75be23d7-424e-4e56-91d2-804fc9333842</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
         <is>
           <t>False</t>
         </is>
